--- a/sample_data/Sample_Results.xlsx
+++ b/sample_data/Sample_Results.xlsx
@@ -425,13 +425,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>student_id</t>
+          <t>enrollment_no</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -447,6 +447,16 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>external_score</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>semester</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>academic_year</t>
         </is>
       </c>
     </row>
@@ -462,10 +472,18 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>26</v>
+        <v>28.5</v>
       </c>
       <c r="D2" t="n">
-        <v>56</v>
+        <v>64</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -480,10 +498,18 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>42</v>
+        <v>58.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -498,10 +524,18 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>36</v>
+        <v>60</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -516,10 +550,18 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D5" t="n">
-        <v>47</v>
+        <v>52</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -534,10 +576,18 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>22.5</v>
       </c>
       <c r="D6" t="n">
-        <v>55</v>
+        <v>48</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -552,10 +602,18 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>55</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -570,10 +628,18 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="D8" t="n">
-        <v>67</v>
+        <v>42</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -588,10 +654,18 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D9" t="n">
-        <v>67</v>
+        <v>38</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -606,388 +680,18 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D10" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>SU2026-0004</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>18</v>
-      </c>
-      <c r="D11" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>SU2026-0004</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>22</v>
-      </c>
-      <c r="D12" t="n">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>SU2026-0004</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>23</v>
-      </c>
-      <c r="D13" t="n">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>SU2026-0005</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>19</v>
-      </c>
-      <c r="D14" t="n">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>SU2026-0005</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>27</v>
-      </c>
-      <c r="D15" t="n">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>SU2026-0005</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>21</v>
-      </c>
-      <c r="D16" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SU2026-0006</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>29</v>
-      </c>
-      <c r="D17" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SU2026-0006</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>21</v>
-      </c>
-      <c r="D18" t="n">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SU2026-0006</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>22</v>
-      </c>
-      <c r="D19" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SU2026-0007</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>18</v>
-      </c>
-      <c r="D20" t="n">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>SU2026-0007</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>20</v>
-      </c>
-      <c r="D21" t="n">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>SU2026-0007</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>20</v>
-      </c>
-      <c r="D22" t="n">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>SU2026-0008</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>16</v>
-      </c>
-      <c r="D23" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>SU2026-0008</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>15</v>
-      </c>
-      <c r="D24" t="n">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SU2026-0008</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>15</v>
-      </c>
-      <c r="D25" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>SU2026-0009</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>17</v>
-      </c>
-      <c r="D26" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>SU2026-0009</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>29</v>
-      </c>
-      <c r="D27" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>SU2026-0009</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>15</v>
-      </c>
-      <c r="D28" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>SU2026-0010</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Physics</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>7</v>
-      </c>
-      <c r="D29" t="n">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>SU2026-0010</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Mathematics</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>21</v>
-      </c>
-      <c r="D30" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>SU2026-0010</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Geography</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>22</v>
-      </c>
-      <c r="D31" t="n">
-        <v>37</v>
+        <v>45</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-27</t>
+        </is>
       </c>
     </row>
   </sheetData>
